--- a/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input_corretto.xlsx
+++ b/tests/realSuite/Piano-Viaggi_-Cadette_i_27-Febbaio-2026_con-Vettore-2/input_corretto.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Damiano Chiesa, Viale Damiano Chiesa, Alboletta, Sant'Alessandro, Riva del Garda, Comunità Alto Garda e Ledro, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38066, Italia</t>
+          <t>Viale Rosmini, Alboletta, Riva del Garda, Comunità Alto Garda e Ledro, Provincia di Trento, Trentino – Alto Adige/Südtirol, 38066, Italy</t>
         </is>
       </c>
       <c r="C21" t="n">
